--- a/output/pdf_financials_xlsx/MERC.xlsx
+++ b/output/pdf_financials_xlsx/MERC.xlsx
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.286638</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.089675</v>
       </c>
     </row>
     <row r="93">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000468</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.320435</v>
+        <v>0.033452</v>
       </c>
     </row>
     <row r="119">
@@ -2652,7 +2652,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.286638</v>
       </c>
@@ -2960,7 +2964,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.000468</v>
       </c>

--- a/output/pdf_financials_xlsx/MERC.xlsx
+++ b/output/pdf_financials_xlsx/MERC.xlsx
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.010662</v>
       </c>
     </row>
     <row r="13">
@@ -797,7 +797,7 @@
         <v>-0.518191</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.57123</v>
+        <v>-2.581892</v>
       </c>
     </row>
     <row r="28">
@@ -823,7 +823,7 @@
         <v>-0.518191</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.57123</v>
+        <v>-2.581892</v>
       </c>
     </row>
     <row r="30">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.728723</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.712088</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.728723</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.712088</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.728723</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.967321</v>
+        <v>0.255233</v>
       </c>
     </row>
     <row r="49">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/MERC.xlsx
+++ b/output/pdf_financials_xlsx/MERC.xlsx
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.01757</v>
+        <v>0.049422</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.24365</v>
+        <v>0.258211</v>
       </c>
     </row>
     <row r="10">
@@ -3836,7 +3836,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.031852</v>
       </c>

--- a/output/pdf_financials_xlsx/MERC.xlsx
+++ b/output/pdf_financials_xlsx/MERC.xlsx
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01699</v>
       </c>
     </row>
     <row r="112">
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01699</v>
       </c>
     </row>
     <row r="135">
@@ -2215,7 +2215,7 @@
         <v>-0.340565</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.633062</v>
+        <v>-1.650052</v>
       </c>
     </row>
   </sheetData>
@@ -2992,7 +2992,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
